--- a/p6_deployment/data/england/data_preparation/format_data/df_match_form.xlsx
+++ b/p6_deployment/data/england/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,803 +480,2805 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>coach_away</t>
+          <t>season</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>country</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
+          <t>competition</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jXP8f29S</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Oliver M. (Eng)</t>
-        </is>
-      </c>
+        <v>45520.66666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Emirates Stadium (London)</t>
+          <t>Old Trafford
+ (Manchester)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60704</v>
+        <v>75635</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester Utd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>arteta mikel</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>dyche sean</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>48</v>
-      </c>
-      <c r="P2" t="n">
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>48</v>
+      </c>
+      <c r="L2" t="n">
         <v>481</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>20232024</v>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>htCzjMHq</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Hooper S. (Eng)</t>
-        </is>
-      </c>
+        <v>45521.35416666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brentford Community Stadium (London)</t>
+          <t>Portman Road
+ (Ipswich)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17250</v>
+        <v>29673</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Newcastle</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>frank thomas</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>howe eddie</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>48</v>
-      </c>
-      <c r="P3" t="n">
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>48</v>
+      </c>
+      <c r="L3" t="n">
         <v>481</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>20232024</v>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pawson C. (Eng)</t>
-        </is>
-      </c>
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amex Stadium (Brighton)</t>
+          <t>Emirates Stadium
+ (London)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31876</v>
+        <v>60704</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>de zerbi roberto</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>ten hag erik</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>48</v>
-      </c>
-      <c r="P4" t="n">
+          <t>Wolves</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>48</v>
+      </c>
+      <c r="L4" t="n">
         <v>481</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>20232024</v>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Scott G. (Eng)</t>
-        </is>
-      </c>
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Turf Moor (Burnley)</t>
+          <t>Goodison Park
+ (Liverpool)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22546</v>
+        <v>39572</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nottingham</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>kompany vincent</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>espirito santo</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>48</v>
-      </c>
-      <c r="P5" t="n">
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L5" t="n">
         <v>481</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>20232024</v>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Taylor A. (Eng)</t>
-        </is>
-      </c>
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stamford Bridge (London)</t>
+          <t>St. James' Park
+ (Newcastle)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40341</v>
+        <v>52305</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>zuJM7XDg</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>pochettino mauricio</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>iraola andoni</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>48</v>
-      </c>
-      <c r="P6" t="n">
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>48</v>
+      </c>
+      <c r="L6" t="n">
         <v>481</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>20232024</v>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bond D. (Eng)</t>
-        </is>
-      </c>
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Selhurst Park (London)</t>
+          <t>City Ground
+ (Nottingham)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25486</v>
+        <v>30404</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>glasner oliver</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>emery unai</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>48</v>
-      </c>
-      <c r="P7" t="n">
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>48</v>
+      </c>
+      <c r="L7" t="n">
         <v>481</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>20232024</v>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Kavanagh C. (Eng)</t>
-        </is>
-      </c>
+        <v>45521.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Anfield (Liverpool)</t>
+          <t>London Stadium
+ (London)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61276</v>
+        <v>62500</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Wolves</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>x6CvOHH9</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>klopp jurgen</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>o neil gary</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>48</v>
-      </c>
-      <c r="P8" t="n">
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>48</v>
+      </c>
+      <c r="L8" t="n">
         <v>481</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>20232024</v>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Donohue M. (Eng)</t>
-        </is>
-      </c>
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kenilworth Road (Luton)</t>
+          <t>Brentford Community Stadium
+ (London)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12300</v>
+        <v>17250</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SlybbadF</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fulham</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>MBpIn2MH</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>edwards rob</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>silva marco</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>48</v>
-      </c>
-      <c r="P9" t="n">
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>48</v>
+      </c>
+      <c r="L9" t="n">
         <v>481</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>20232024</v>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brooks J. (Eng)</t>
-        </is>
-      </c>
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Etihad Stadium (Manchester)</t>
+          <t>Wembley Stadium
+ (London)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>55097</v>
+        <v>90000</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Manchester Utd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Wtn9Stg0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>West Ham</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>guardiola pep</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>hUGEt9yf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>moyes david</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>48</v>
-      </c>
-      <c r="P10" t="n">
-        <v>481</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>20232024</v>
+      <c r="K10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L10" t="n">
+        <v>482</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FA Community Shield</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45431.5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Madley A. (Eng)</t>
-        </is>
-      </c>
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bramall Lane (Sheffield)</t>
+          <t>Brunton Park
+ (Carlisle)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>32050</v>
+        <v>17949</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>dUzTIwSF</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Carlisle</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Stoke</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>48</v>
+      </c>
+      <c r="L11" t="n">
+        <v>484</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Brisbane Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>9271</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KKyYcus9</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ChwgcrNJ</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Newport</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L12" t="n">
+        <v>484</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Edgeley Park
+ (Stockport)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10841</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IX6WjNvr</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Stockport County</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>48</v>
+      </c>
+      <c r="L13" t="n">
+        <v>484</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Holker Street
+ (Barrow in Furness)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KKJL7QXd</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>U3lM3y4e</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>48</v>
+      </c>
+      <c r="L14" t="n">
+        <v>484</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Toughsheet Community Stadium
+ (Bolton)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28723</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Or1bBrWD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bolton</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>t6G9wMZN</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Mansfield</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>48</v>
+      </c>
+      <c r="L15" t="n">
+        <v>484</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ashton Gate Stadium
+ (Bristol)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>48</v>
+      </c>
+      <c r="L16" t="n">
+        <v>484</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hayes Lane
+ (London)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Opdcd08Q</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4KREuF43</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>48</v>
+      </c>
+      <c r="L17" t="n">
+        <v>484</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pirelli Stadium
+ (Burton upon Trent)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6912</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nwCtJaJT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8EFIJthC</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Blackpool</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" t="n">
+        <v>484</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Abbey Stadium
+ (Cambridge)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>7937</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>lnb8EJRp</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Cambridge Utd</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>48</v>
+      </c>
+      <c r="L19" t="n">
+        <v>484</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>33280</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>GILi6JC9</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>48</v>
+      </c>
+      <c r="L20" t="n">
+        <v>484</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>The Valley
+ (London)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>27111</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>fXf5mQ7t</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Charlton</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SWk4muv7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>48</v>
+      </c>
+      <c r="L21" t="n">
+        <v>484</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Colchester Community Stadium
+ (Colchester)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>10105</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>xYu73rNn</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EmlVDpVP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>48</v>
+      </c>
+      <c r="L22" t="n">
+        <v>484</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The Broadfield Stadium
+ (Crawley)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6134</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>QVmLl54o</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Crawley</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>xSloasB8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Swindon</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>48</v>
+      </c>
+      <c r="L23" t="n">
+        <v>484</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pride Park
+ (Derby)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>33597</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>dQIMIN5n</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>48</v>
+      </c>
+      <c r="L24" t="n">
+        <v>484</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Highbury Stadium
+ (Fleetwood)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5327</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tCZ3D68d</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fleetwood</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>48</v>
+      </c>
+      <c r="L25" t="n">
+        <v>484</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Blundell Park
+ (Cleethorpes)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>9052</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>OEaiS3za</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>bsc3EJ27</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Bradford City</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>48</v>
+      </c>
+      <c r="L26" t="n">
+        <v>484</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>John Smith's Stadium
+ (Huddersfield)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24121</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Huddersfield</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>zmKRcPKu</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Morecambe</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>48</v>
+      </c>
+      <c r="L27" t="n">
+        <v>484</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LNER stadium
+ (Lincoln)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>10669</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>hrHTRs5B</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CQv5qrFt</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Harrogate</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>48</v>
+      </c>
+      <c r="L28" t="n">
+        <v>484</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sixfields Stadium
+ (Northampton)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>7798</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>l4P6dwRR</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Northampton</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>hl2V5JIl</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Wycombe</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>48</v>
+      </c>
+      <c r="L29" t="n">
+        <v>484</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Carrow Road
+ (Norwich)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>27137</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ANwyQM2M</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Stevenage</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>48</v>
+      </c>
+      <c r="L30" t="n">
+        <v>484</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Kassam Stadium
+ (Oxford)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>tWeI85kh</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Peterborough</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>48</v>
+      </c>
+      <c r="L31" t="n">
+        <v>484</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fratton Park
+ (Portsmouth)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>21944</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>48</v>
+      </c>
+      <c r="L32" t="n">
+        <v>484</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>23408</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>48</v>
+      </c>
+      <c r="L33" t="n">
+        <v>484</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Aesseal New York Stadium
+ (Rotherham)</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>12021</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>KMfM7P4b</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>YacqHHdS</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Crewe</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>48</v>
+      </c>
+      <c r="L34" t="n">
+        <v>484</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Peninsula Stadium
+ (Salford)</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5108</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>W4AadhN3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Salford</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>hlzYDy5q</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Doncaster</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>48</v>
+      </c>
+      <c r="L35" t="n">
+        <v>484</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The Croud Meadow
+ (Shrewsbury)</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>9877</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>EqfQ6qK4</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>EwJVdqzn</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Notts Co</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>48</v>
+      </c>
+      <c r="L36" t="n">
+        <v>484</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>WvZyDeKk</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>48</v>
+      </c>
+      <c r="L37" t="n">
+        <v>484</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Prenton Park
+ (Birkenhead)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>16587</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>jVhkb1QE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tranmere</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6ZvdGuYf</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Accrington</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>48</v>
+      </c>
+      <c r="L38" t="n">
+        <v>484</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bescot Stadium
+ (Walsall)</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>YgrfcLuL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ve14a3l4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Exeter</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>48</v>
+      </c>
+      <c r="L39" t="n">
+        <v>484</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>f9KDxtkU</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>MK Dons</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>48</v>
+      </c>
+      <c r="L40" t="n">
+        <v>484</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DW Stadium
+ (Wigan)</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>25133</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MgHlK2Na</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Wigan</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>UNGEKMx6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>48</v>
+      </c>
+      <c r="L41" t="n">
+        <v>484</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45517.66666666666</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>32050</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>MeKPSerA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Sheffield Utd</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Tottenham</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>wilder chris</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>postecoglou ange</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>48</v>
-      </c>
-      <c r="P11" t="n">
-        <v>481</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>20232024</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>IgO7K1ZA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>48</v>
+      </c>
+      <c r="L42" t="n">
+        <v>484</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>25586</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Hull</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sheffield Wed</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>48</v>
+      </c>
+      <c r="L43" t="n">
+        <v>484</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Home Park
+ (Plymouth)</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>jizXHcsM</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>48</v>
+      </c>
+      <c r="L44" t="n">
+        <v>484</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>37792</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>48</v>
+      </c>
+      <c r="L45" t="n">
+        <v>484</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>EFL Cup</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/data_preparation/format_data/df_match_form.xlsx
+++ b/p6_deployment/data/england/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,2266 +1016,2392 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45522.52083333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L10" t="n">
+        <v>481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AeRSxQrK</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45523.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>48</v>
+      </c>
+      <c r="L11" t="n">
+        <v>481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Wembley Stadium
  (London)</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" t="n">
         <v>90000</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Manchester Utd</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Wtn9Stg0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>48</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L12" t="n">
         <v>482</v>
       </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
         <v>2024</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>FA Community Shield</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>OMDVg8x9</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Brunton Park
  (Carlisle)</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E13" t="n">
         <v>17949</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>dUzTIwSF</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Carlisle</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>hSUajdSS</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Stoke</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>48</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K13" t="n">
+        <v>48</v>
+      </c>
+      <c r="L13" t="n">
         <v>484</v>
       </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>jXcAnQUr</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Brisbane Road
  (London)</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E14" t="n">
         <v>9271</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>KKyYcus9</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Leyton Orient</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>ChwgcrNJ</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Newport</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>48</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="K14" t="n">
+        <v>48</v>
+      </c>
+      <c r="L14" t="n">
         <v>484</v>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>fRe0c20b</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Edgeley Park
  (Stockport)</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>10841</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>IX6WjNvr</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Stockport County</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>6Nl8nagD</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Blackburn</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>48</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K15" t="n">
+        <v>48</v>
+      </c>
+      <c r="L15" t="n">
         <v>484</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>CnnJp4ae</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Holker Street
  (Barrow in Furness)</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>6500</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>KKJL7QXd</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Barrow</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>U3lM3y4e</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Port Vale</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>48</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K16" t="n">
+        <v>48</v>
+      </c>
+      <c r="L16" t="n">
         <v>484</v>
       </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>bw1zAKS6</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Toughsheet Community Stadium
  (Bolton)</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E17" t="n">
         <v>28723</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Or1bBrWD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Bolton</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>t6G9wMZN</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Mansfield</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>48</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K17" t="n">
+        <v>48</v>
+      </c>
+      <c r="L17" t="n">
         <v>484</v>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>GINCsvmn</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Ashton Gate Stadium
  (Bristol)</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E18" t="n">
         <v>27000</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>MahqU27I</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Bristol City</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>GOvB22xg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Coventry</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>48</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K18" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" t="n">
         <v>484</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>x6klsVh3</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Hayes Lane
  (London)</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E19" t="n">
         <v>5000</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Opdcd08Q</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Bromley</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>4KREuF43</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>AFC Wimbledon</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>48</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K19" t="n">
+        <v>48</v>
+      </c>
+      <c r="L19" t="n">
         <v>484</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>b3pRrrU7</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Pirelli Stadium
  (Burton upon Trent)</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E20" t="n">
         <v>6912</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>nwCtJaJT</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Burton</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>8EFIJthC</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Blackpool</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>48</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K20" t="n">
+        <v>48</v>
+      </c>
+      <c r="L20" t="n">
         <v>484</v>
       </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>WfkfPdXH</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Abbey Stadium
  (Cambridge)</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E21" t="n">
         <v>7937</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>lnb8EJRp</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Cambridge Utd</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>lrMHUHDc</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>QPR</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>48</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K21" t="n">
+        <v>48</v>
+      </c>
+      <c r="L21" t="n">
         <v>484</v>
       </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>SMr3Nz2U</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Cardiff City Stadium
  (Cardiff)</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E22" t="n">
         <v>33280</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>hO8wh6aP</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Cardiff</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>GILi6JC9</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Bristol Rovers</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>48</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="K22" t="n">
+        <v>48</v>
+      </c>
+      <c r="L22" t="n">
         <v>484</v>
       </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>xYBLuIHb</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>The Valley
  (London)</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E23" t="n">
         <v>27111</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>fXf5mQ7t</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Charlton</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>SWk4muv7</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>48</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K23" t="n">
+        <v>48</v>
+      </c>
+      <c r="L23" t="n">
         <v>484</v>
       </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>6os5wmhS</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Colchester Community Stadium
  (Colchester)</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>10105</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>xYu73rNn</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Colchester</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>EmlVDpVP</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Reading</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>48</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K24" t="n">
+        <v>48</v>
+      </c>
+      <c r="L24" t="n">
         <v>484</v>
       </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Kl7vhn7L</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>The Broadfield Stadium
  (Crawley)</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>6134</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>QVmLl54o</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Crawley</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>xSloasB8</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Swindon</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>48</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K25" t="n">
+        <v>48</v>
+      </c>
+      <c r="L25" t="n">
         <v>484</v>
       </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>nw6fJO5K</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Pride Park
  (Derby)</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>33597</v>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Iug0YO0Q</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Derby</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>dQIMIN5n</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Chesterfield</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>48</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K26" t="n">
+        <v>48</v>
+      </c>
+      <c r="L26" t="n">
         <v>484</v>
       </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>bHPacsq1</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Highbury Stadium
  (Fleetwood)</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>5327</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>tCZ3D68d</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Fleetwood</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>CCBWpzjj</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>West Brom</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>48</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K27" t="n">
+        <v>48</v>
+      </c>
+      <c r="L27" t="n">
         <v>484</v>
       </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>MwmHgKaN</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Blundell Park
  (Cleethorpes)</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>9052</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>OEaiS3za</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Grimsby</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>bsc3EJ27</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Bradford City</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>48</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K28" t="n">
+        <v>48</v>
+      </c>
+      <c r="L28" t="n">
         <v>484</v>
       </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>lQl9etVA</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>John Smith's Stadium
  (Huddersfield)</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E29" t="n">
         <v>24121</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>xxxpBZl2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Huddersfield</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>zmKRcPKu</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Morecambe</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>48</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K29" t="n">
+        <v>48</v>
+      </c>
+      <c r="L29" t="n">
         <v>484</v>
       </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>KWD8eLDD</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>LNER stadium
  (Lincoln)</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E30" t="n">
         <v>10669</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>hrHTRs5B</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Lincoln</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>CQv5qrFt</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Harrogate</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>48</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K30" t="n">
+        <v>48</v>
+      </c>
+      <c r="L30" t="n">
         <v>484</v>
       </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>xUXzYQFk</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Sixfields Stadium
  (Northampton)</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E31" t="n">
         <v>7798</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>l4P6dwRR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Northampton</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>hl2V5JIl</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Wycombe</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>48</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K31" t="n">
+        <v>48</v>
+      </c>
+      <c r="L31" t="n">
         <v>484</v>
       </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>CCV9JR0d</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Carrow Road
  (Norwich)</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E32" t="n">
         <v>27137</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Qo6off6p</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Norwich</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>ANwyQM2M</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Stevenage</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>48</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K32" t="n">
+        <v>48</v>
+      </c>
+      <c r="L32" t="n">
         <v>484</v>
       </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>bsinRI25</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Kassam Stadium
  (Oxford)</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E33" t="n">
         <v>12500</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>vgOBT43c</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Oxford Utd</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>tWeI85kh</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Peterborough</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>48</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K33" t="n">
+        <v>48</v>
+      </c>
+      <c r="L33" t="n">
         <v>484</v>
       </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>GbaVU03t</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Fratton Park
  (Portsmouth)</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E34" t="n">
         <v>21944</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>zckREQFJ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Portsmouth</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>6uz2cJBL</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Millwall</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>48</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K34" t="n">
+        <v>48</v>
+      </c>
+      <c r="L34" t="n">
         <v>484</v>
       </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>tOTmlbNp</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B35" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Deepdale
  (Preston)</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E35" t="n">
         <v>23408</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>x8IDVcbi</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Preston</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>WSzc94ws</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Sunderland</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>48</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K35" t="n">
+        <v>48</v>
+      </c>
+      <c r="L35" t="n">
         <v>484</v>
       </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>nPQL4PjR</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Aesseal New York Stadium
  (Rotherham)</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E36" t="n">
         <v>12021</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>KMfM7P4b</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Rotherham</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>YacqHHdS</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Crewe</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>48</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K36" t="n">
+        <v>48</v>
+      </c>
+      <c r="L36" t="n">
         <v>484</v>
       </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>pWhdu9NF</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Peninsula Stadium
  (Salford)</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E37" t="n">
         <v>5108</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>W4AadhN3</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Salford</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>hlzYDy5q</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Doncaster</t>
         </is>
       </c>
-      <c r="K35" t="n">
-        <v>48</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="K37" t="n">
+        <v>48</v>
+      </c>
+      <c r="L37" t="n">
         <v>484</v>
       </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>6NnRD2Ts</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B38" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>The Croud Meadow
  (Shrewsbury)</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E38" t="n">
         <v>9877</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>EqfQ6qK4</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Shrewsbury</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>EwJVdqzn</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Notts Co</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>48</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="K38" t="n">
+        <v>48</v>
+      </c>
+      <c r="L38" t="n">
         <v>484</v>
       </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>2FcwTvYh</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Swansea.com Stadium
  (Swansea)</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E39" t="n">
         <v>21088</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>K6xezbY7</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Swansea</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>WvZyDeKk</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Gillingham</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>48</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="K39" t="n">
+        <v>48</v>
+      </c>
+      <c r="L39" t="n">
         <v>484</v>
       </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>EBSD6oME</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Prenton Park
  (Birkenhead)</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E40" t="n">
         <v>16587</v>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>jVhkb1QE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Tranmere</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>6ZvdGuYf</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Accrington</t>
         </is>
       </c>
-      <c r="K38" t="n">
-        <v>48</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="K40" t="n">
+        <v>48</v>
+      </c>
+      <c r="L40" t="n">
         <v>484</v>
       </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>WSQqW4p2</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B41" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Bescot Stadium
  (Walsall)</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E41" t="n">
         <v>11300</v>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>YgrfcLuL</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Walsall</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>ve14a3l4</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Exeter</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>48</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="K41" t="n">
+        <v>48</v>
+      </c>
+      <c r="L41" t="n">
         <v>484</v>
       </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>vaX1LmWq</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B42" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Vicarage Road
  (Watford)</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E42" t="n">
         <v>22200</v>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>UmMRoGzp</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Watford</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>f9KDxtkU</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>MK Dons</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>48</v>
-      </c>
-      <c r="L40" t="n">
+      <c r="K42" t="n">
+        <v>48</v>
+      </c>
+      <c r="L42" t="n">
         <v>484</v>
       </c>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>n1hhaOVo</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B43" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>DW Stadium
  (Wigan)</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E43" t="n">
         <v>25133</v>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>MgHlK2Na</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Wigan</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>UNGEKMx6</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Barnsley</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>48</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="K43" t="n">
+        <v>48</v>
+      </c>
+      <c r="L43" t="n">
         <v>484</v>
       </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>vyoZBtbf</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B44" s="2" t="n">
         <v>45517.66666666666</v>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Bramall Lane
  (Sheffield)</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E44" t="n">
         <v>32050</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>MeKPSerA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Sheffield Utd</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>IgO7K1ZA</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Wrexham</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>48</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="K44" t="n">
+        <v>48</v>
+      </c>
+      <c r="L44" t="n">
         <v>484</v>
       </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>634r8bcJ</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B45" s="2" t="n">
         <v>45518.65625</v>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t>MKM Stadium
  (Hull)</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E45" t="n">
         <v>25586</v>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>S66R0t75</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Hull</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>llcCvIcG</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Sheffield Wed</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>48</v>
-      </c>
-      <c r="L43" t="n">
+      <c r="K45" t="n">
+        <v>48</v>
+      </c>
+      <c r="L45" t="n">
         <v>484</v>
       </c>
-      <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>pbFTwdnB</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B46" s="2" t="n">
         <v>45518.65625</v>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Home Park
  (Plymouth)</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E46" t="n">
         <v>17000</v>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>WpGM6ELj</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Plymouth</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>jizXHcsM</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Cheltenham</t>
         </is>
       </c>
-      <c r="K44" t="n">
-        <v>48</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="K46" t="n">
+        <v>48</v>
+      </c>
+      <c r="L46" t="n">
         <v>484</v>
       </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B47" s="2" t="n">
         <v>45518.66666666666</v>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Elland Road
  (Leeds)</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E47" t="n">
         <v>37792</v>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>tUxUbLR2</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Leeds</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>6F0lvLNC</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Middlesbrough</t>
         </is>
       </c>
-      <c r="K45" t="n">
-        <v>48</v>
-      </c>
-      <c r="L45" t="n">
+      <c r="K47" t="n">
+        <v>48</v>
+      </c>
+      <c r="L47" t="n">
         <v>484</v>
       </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>EFL Cup</t>
         </is>
